--- a/prototype/本周进度监控表_0803-0809.xlsx
+++ b/prototype/本周进度监控表_0803-0809.xlsx
@@ -657,7 +657,7 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>M1组（杨胜威、宋丽娜）→ 模块一 签到情绪    |    M2组（师润佳、郑永涛）→ 模块二 脑力游戏</t>
+          <t>M1组（杨胜威、宋丽娜）→ 模块一 签到情绪    |    M2组（郑永涛、师润佳）→ 模块二 脑力游戏</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -1812,7 +1812,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>M2 脑力游戏组 — 师润佳(后端) / 郑永涛(前端)</t>
+          <t>M2 脑力游戏组 — 郑永涛(后端) / 师润佳(前端)</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>师润佳（后端）</t>
+          <t>郑永涛（后端）</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>郑永涛（前端）</t>
+          <t>师润佳（前端）</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr"/>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr"/>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr"/>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr"/>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr"/>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr"/>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr"/>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>师润佳</t>
+          <t>郑永涛</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>师润佳+郑永涛</t>
+          <t>郑永涛+师润佳</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>郑永涛</t>
+          <t>师润佳</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
